--- a/.xlsx files/Andah_Janus Statistics.xlsx
+++ b/.xlsx files/Andah_Janus Statistics.xlsx
@@ -2187,7 +2187,7 @@
     <t>Pekan</t>
   </si>
   <si>
-    <t>lasri</t>
+    <t>Lasri</t>
   </si>
   <si>
     <t>LAHS-ree</t>
